--- a/healthcare_surveys/013_healthcare_appointment_scheduling_process_poll--healthcare_surveys.xlsx
+++ b/healthcare_surveys/013_healthcare_appointment_scheduling_process_poll--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'appointment',_'label':_'appointment'}</t>
+          <t>appointment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Appointment', 'label': 'Appointment'}</t>
+          <t>Appointment</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'walk-in',_'label':_'walk-in'}</t>
+          <t>walk-in</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Walk-in', 'label': 'Walk-in'}</t>
+          <t>Walk-in</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'no-show',_'label':_'no-show'}</t>
+          <t>no-show</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'No-show', 'label': 'No-show'}</t>
+          <t>No-show</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online_scheduling',_'label':_'online_scheduling'}</t>
+          <t>online_scheduling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online Scheduling', 'label': 'Online Scheduling'}</t>
+          <t>Online Scheduling</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'call_center',_'label':_'call_center'}</t>
+          <t>call_center</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Call Center', 'label': 'Call Center'}</t>
+          <t>Call Center</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'walk-in',_'label':_'walk-in'}</t>
+          <t>walk-in</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Walk-in', 'label': 'Walk-in'}</t>
+          <t>Walk-in</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'other_(please_specify)',_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Other (please specify)', 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monday',_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Monday', 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tuesday',_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tuesday', 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wednesday',_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Wednesday', 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'thursday',_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Thursday', 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'friday',_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Friday', 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'saturday',_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Saturday', 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'sunday',_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Sunday', 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Somewhat Satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'neither_satisfied',_'label':_'neither_satisfied'}</t>
+          <t>neither_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Neither Satisfied', 'label': 'Neither Satisfied'}</t>
+          <t>Neither Satisfied</t>
         </is>
       </c>
     </row>
